--- a/artfynd/A 10224-2026 artfynd.xlsx
+++ b/artfynd/A 10224-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110353286</v>
+        <v>101064275</v>
       </c>
       <c r="B2" t="n">
-        <v>106457</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>231235</v>
+        <v>102118</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Narrklibbfibbla</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hieracium chlorodes</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dahlst.) Dahlst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tönnersjö, 150 m SSV Bygdegården, Hl</t>
+          <t>Halmstad, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379992.5271192961</v>
+        <v>379678</v>
       </c>
       <c r="R2" t="n">
-        <v>6277938.192996203</v>
+        <v>6277582</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,29 +778,633 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Gräsrik vägkant mot blandskog</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Kjell Georgson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Robin Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Robin Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109711725</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Perstorp, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>379675</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6277583</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tönnersjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>23:06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>23:06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Göran Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109767334</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Perstorp Skogstomten, Halmstad, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>379628</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6277527</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tönnersjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annelie Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annelie Larsson, Elin Lundgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>88489232</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tönnersjövägen, 750 m NO Perstorpskrysset, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>379422</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6277305</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tönnersjö</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Arkiv-N-Hal-0874</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-05-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-05-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Magnusson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Magnusson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110353286</v>
+      </c>
+      <c r="B6" t="n">
+        <v>109564</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>231235</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Narrklibbfibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hieracium chlorodes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dahlst.) Dahlst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tönnersjö, 150 m SSV Bygdegården, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>379993</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6277938</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tönnersjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gräsrik vägkant mot blandskog</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
           <t>Kjell Georgson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AR6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
         <is>
           <t>Kjell Georgson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102207207</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109784</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>231446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hallandsfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hieracium subterdentatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Johanss. &amp; Sam.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tönnersjö, 150 m SSV Bygdegården, vägkant, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>379998</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6277934</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tönnersjö</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>N-Hal-1673</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Medobservatör Bitte Georgson</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gräsrik vägkant mot blandskog</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
